--- a/artifacts/school-financial-model/public/proof_workbook.xlsx
+++ b/artifacts/school-financial-model/public/proof_workbook.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="237">
   <si>
     <t>SchoolStack — Underwriting Assumptions</t>
   </si>
@@ -383,13 +383,37 @@
     <t>USES OF FUNDS</t>
   </si>
   <si>
-    <t>No capital expenditures entered</t>
+    <t>Deposits &amp; Prepaid Occupancy (2 mo)</t>
+  </si>
+  <si>
+    <t>Occupancy / Facility Costs (Year 1)</t>
+  </si>
+  <si>
+    <t>Equipment / FF&amp;E / Technology</t>
+  </si>
+  <si>
+    <t>Curriculum &amp; Program Launch Costs</t>
+  </si>
+  <si>
+    <t>Professional Fees &amp; Administration</t>
+  </si>
+  <si>
+    <t>Year 1 Debt Service</t>
+  </si>
+  <si>
+    <t>Working Capital Reserve (2 mo)</t>
+  </si>
+  <si>
+    <t>Contingency (5%)</t>
   </si>
   <si>
     <t>TOTAL USES</t>
   </si>
   <si>
     <t>SOURCES − USES (SURPLUS / GAP)</t>
+  </si>
+  <si>
+    <t>⚠ Funding gap — additional sources needed</t>
   </si>
   <si>
     <t>SchoolStack — Debt Schedule</t>
@@ -725,7 +749,7 @@
     <numFmt numFmtId="168" formatCode="0.00x"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -757,6 +781,12 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FFD32F2F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -827,7 +857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -851,6 +881,8 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -860,8 +892,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1409,7 +1441,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B2" s="9">
         <v>177100</v>
@@ -1429,7 +1461,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B3" s="12">
         <v>140501</v>
@@ -1449,7 +1481,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B4" s="12">
         <v>58200</v>
@@ -1469,7 +1501,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B5" s="12">
         <v>12023</v>
@@ -1489,7 +1521,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B6" s="20">
         <f>SUM(B3:B5)</f>
@@ -1514,7 +1546,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B7" s="9">
         <f>B2-B6</f>
@@ -1539,7 +1571,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B8" s="11">
         <f>IF(B2=0,0,B7/B2)</f>
@@ -1564,7 +1596,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B9" s="9">
         <f>B7</f>
@@ -1624,7 +1656,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1634,7 +1666,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B3" s="12">
         <v>16377</v>
@@ -1654,7 +1686,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B4" s="12">
         <v>0</v>
@@ -1674,7 +1706,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B5" s="13">
         <f>SUM(B3:B4)</f>
@@ -1699,7 +1731,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1709,7 +1741,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B8" s="12">
         <v>41727</v>
@@ -1729,7 +1761,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B9" s="12">
         <v>0</v>
@@ -1749,7 +1781,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B10" s="13">
         <f>SUM(B8:B9)</f>
@@ -1774,7 +1806,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1784,7 +1816,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B13" s="12">
         <v>0</v>
@@ -1804,7 +1836,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B14" s="12">
         <v>-25350</v>
@@ -1824,7 +1856,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B15" s="13">
         <f>B5-B10</f>
@@ -1849,7 +1881,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B17" s="9">
         <f>B5-B10-B15</f>
@@ -1909,7 +1941,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1919,7 +1951,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B3" s="12">
         <v>-21601</v>
@@ -1939,7 +1971,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B4" s="12">
         <v>12023</v>
@@ -1959,32 +1991,32 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="22">
+        <v>188</v>
+      </c>
+      <c r="B5" s="24">
         <f>IF(B4=0,"N/A",B3/B4)</f>
         <v>-1.7966397737669466</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="24">
         <f>IF(C4=0,"N/A",C3/C4)</f>
         <v>0.3251268402229061</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="24">
         <f>IF(D4=0,"N/A",D3/D4)</f>
         <v>3.039923479996673</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="24">
         <f>IF(E4=0,"N/A",E3/E4)</f>
         <v>6.633036679697247</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="24">
         <f>IF(F4=0,"N/A",F3/F4)</f>
         <v>10.511436413540714</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1994,7 +2026,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B8" s="12">
         <v>16377</v>
@@ -2014,7 +2046,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B9" s="12">
         <v>16558</v>
@@ -2034,32 +2066,32 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B10" s="23">
+        <v>192</v>
+      </c>
+      <c r="B10" s="25">
         <f>IF(B9=0,0,B8/B9)</f>
         <v>0.9890687281072593</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="25">
         <f>IF(C9=0,0,C8/C9)</f>
         <v>0.4909404146616765</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="25">
         <f>IF(D9=0,0,D8/D9)</f>
         <v>1.9120116618075802</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="25">
         <f>IF(E9=0,0,E8/E9)</f>
         <v>5.74290121693424</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="25">
         <f>IF(F9=0,0,F8/F9)</f>
         <v>12.009557344064387</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B11" s="12">
         <v>30</v>
@@ -2079,7 +2111,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2089,82 +2121,82 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>189</v>
+        <v>195</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>189</v>
+        <v>198</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>189</v>
+        <v>199</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>189</v>
+        <v>200</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2184,65 +2216,65 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
+      <c r="A1" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
+      <c r="A2" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>188</v>
-      </c>
       <c r="C5" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>188</v>
+        <v>206</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>196</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>188</v>
+        <v>208</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>196</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>189</v>
+        <v>210</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>197</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>31</v>
@@ -2250,59 +2282,59 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>188</v>
+        <v>211</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>196</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>189</v>
+        <v>213</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>197</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>211</v>
+        <v>218</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B17" s="5">
         <v>177100</v>
@@ -2310,7 +2342,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B18" s="5">
         <v>210724</v>
@@ -2318,7 +2350,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B19" s="5">
         <v>-33623</v>
@@ -2326,7 +2358,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B20" s="6">
         <v>-0.1898531902879729</v>
@@ -2334,7 +2366,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B21" s="5">
         <v>50000</v>
@@ -2342,7 +2374,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B22" s="5">
         <v>16377</v>
@@ -2350,7 +2382,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B23" s="5">
         <v>50000</v>
@@ -2358,23 +2390,23 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>31</v>
@@ -2382,7 +2414,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B27" s="5">
         <v>9839</v>
@@ -2390,7 +2422,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B28" s="5">
         <v>11707</v>
@@ -2417,7 +2449,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2467,7 +2499,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B5" s="9">
         <v>177100</v>
@@ -2487,7 +2519,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B6" s="12">
         <v>140501</v>
@@ -2507,7 +2539,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B7" s="12">
         <v>58200</v>
@@ -2527,7 +2559,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B8" s="12">
         <v>12023</v>
@@ -2547,7 +2579,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B9" s="20">
         <v>210724</v>
@@ -2567,7 +2599,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B10" s="9">
         <v>-33623</v>
@@ -2587,7 +2619,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B11" s="11">
         <v>-0.1898531902879729</v>
@@ -2607,7 +2639,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B12" s="9">
         <v>-33623</v>
@@ -2627,7 +2659,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B13" s="9">
         <v>16377</v>
@@ -2647,7 +2679,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B14" s="12">
         <v>9839</v>
@@ -2687,21 +2719,21 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B16" s="22">
+        <v>188</v>
+      </c>
+      <c r="B16" s="24">
         <v>-1.8</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="24">
         <v>0.33</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="24">
         <v>3.04</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="24">
         <v>6.63</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="24">
         <v>10.51</v>
       </c>
     </row>
@@ -4018,10 +4050,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4041,7 +4073,7 @@
       <c r="A4" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="15">
         <v>0</v>
       </c>
     </row>
@@ -4078,28 +4110,97 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="15">
+        <v>140501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="15">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="20">
-        <f>SUM(B10:B10)</f>
-        <v>0</v>
+      <c r="B12" s="15">
+        <v>34200</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B13" s="5">
-        <f>B7-B11</f>
-        <v>227100</v>
+      <c r="B13" s="15">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="15">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="15">
+        <v>12600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="15">
+        <v>12023</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="15">
+        <v>33117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="15">
+        <v>12417</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" s="20">
+        <f>SUM(B10:B18)</f>
+        <v>260758</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" s="21">
+        <f>B7-B19</f>
+        <v>-33658</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4124,7 +4225,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4135,30 +4236,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B4" s="12">
         <v>50000</v>
@@ -4166,7 +4267,7 @@
       <c r="C4" s="11">
         <v>0.075</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="23">
         <v>5</v>
       </c>
       <c r="E4" s="12">
@@ -4181,7 +4282,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -4192,7 +4293,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B7" s="5">
         <v>12023</v>
@@ -4200,7 +4301,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B8" s="17">
         <v>1002</v>
@@ -4208,7 +4309,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -4219,10 +4320,10 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4292,45 +4393,45 @@
         <v>15</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B2" s="12">
         <v>7000</v>
@@ -4375,7 +4476,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B3" s="12">
         <v>11708</v>
@@ -4420,7 +4521,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B4" s="12">
         <v>4850</v>
@@ -4465,7 +4566,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B5" s="12">
         <v>1002</v>
@@ -4510,7 +4611,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B6" s="20">
         <f>SUM(B3:B5)</f>
@@ -4567,7 +4668,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B7" s="9">
         <f>B2-B6</f>
@@ -4624,7 +4725,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B8" s="9">
         <f>50000+B7</f>
@@ -4681,7 +4782,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -4699,7 +4800,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B11" s="17">
         <v>50000</v>
@@ -4707,7 +4808,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B12" s="5">
         <f>M8</f>
@@ -4716,7 +4817,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B13" s="17">
         <f>MIN(B8:M8)</f>

--- a/artifacts/school-financial-model/public/proof_workbook.xlsx
+++ b/artifacts/school-financial-model/public/proof_workbook.xlsx
@@ -1575,23 +1575,23 @@
       </c>
       <c r="B8" s="11">
         <f>IF(B2=0,0,B7/B2)</f>
-        <v>-0.1898531902879729</v>
+        <v>-0.19</v>
       </c>
       <c r="C8" s="11">
         <f>IF(C2=0,0,C7/C2)</f>
-        <v>-0.0394026226323458</v>
+        <v>-0.04</v>
       </c>
       <c r="D8" s="11">
         <f>IF(D2=0,0,D7/D2)</f>
-        <v>0.10120486899112853</v>
+        <v>0.1</v>
       </c>
       <c r="E8" s="11">
         <f>IF(E2=0,0,E7/E2)</f>
-        <v>0.23371465051676243</v>
+        <v>0.23</v>
       </c>
       <c r="F8" s="11">
         <f>IF(F2=0,0,F7/F2)</f>
-        <v>0.3352791134044799</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1995,23 +1995,23 @@
       </c>
       <c r="B5" s="24">
         <f>IF(B4=0,"N/A",B3/B4)</f>
-        <v>-1.7966397737669466</v>
+        <v>-1.8</v>
       </c>
       <c r="C5" s="24">
         <f>IF(C4=0,"N/A",C3/C4)</f>
-        <v>0.3251268402229061</v>
+        <v>0.33</v>
       </c>
       <c r="D5" s="24">
         <f>IF(D4=0,"N/A",D3/D4)</f>
-        <v>3.039923479996673</v>
+        <v>3.04</v>
       </c>
       <c r="E5" s="24">
         <f>IF(E4=0,"N/A",E3/E4)</f>
-        <v>6.633036679697247</v>
+        <v>6.63</v>
       </c>
       <c r="F5" s="24">
         <f>IF(F4=0,"N/A",F3/F4)</f>
-        <v>10.511436413540714</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2070,23 +2070,23 @@
       </c>
       <c r="B10" s="25">
         <f>IF(B9=0,0,B8/B9)</f>
-        <v>0.9890687281072593</v>
+        <v>0.99</v>
       </c>
       <c r="C10" s="25">
         <f>IF(C9=0,0,C8/C9)</f>
-        <v>0.4909404146616765</v>
+        <v>0.49</v>
       </c>
       <c r="D10" s="25">
         <f>IF(D9=0,0,D8/D9)</f>
-        <v>1.9120116618075802</v>
+        <v>1.91</v>
       </c>
       <c r="E10" s="25">
         <f>IF(E9=0,0,E8/E9)</f>
-        <v>5.74290121693424</v>
+        <v>5.74</v>
       </c>
       <c r="F10" s="25">
         <f>IF(F9=0,0,F8/F9)</f>
-        <v>12.009557344064387</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="C3" s="11">
         <f>IF(B2=0,"—",(C2-B2)/B2)</f>
-        <v>0.2222222222222222</v>
+        <v>0.22</v>
       </c>
       <c r="D3" s="11">
         <f>IF(C2=0,"—",(D2-C2)/C2)</f>
-        <v>0.18181818181818182</v>
+        <v>0.18</v>
       </c>
       <c r="E3" s="11">
         <f>IF(D2=0,"—",(E2-D2)/D2)</f>
-        <v>0.19230769230769232</v>
+        <v>0.19</v>
       </c>
       <c r="F3" s="11">
         <f>IF(E2=0,"—",(F2-E2)/E2)</f>
-        <v>0.16129032258064516</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
